--- a/NSM_IBSA_2028.xlsx
+++ b/NSM_IBSA_2028.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francesco/DocEvents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FE7B7A-4898-0F4A-8A64-A53AEBFA317A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{641BE98C-39E1-754A-A9FB-631BDEA7A99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60" yWindow="1560" windowWidth="35600" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1120" windowWidth="35600" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Submitted proposal" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4567" uniqueCount="1943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4567" uniqueCount="1971">
   <si>
     <t>NSM IBSA 2028</t>
   </si>
@@ -9090,6 +9090,90 @@
   <si>
     <t>Why Dallas - Top 10</t>
   </si>
+  <si>
+    <t>http://www.hilton.com/en/hotels/sathchf-hilton-san-antonio-hill-country/</t>
+  </si>
+  <si>
+    <t>http://www.hilton.com/en/hotels/phxsppr-hilton-phoenix-resort-at-the-peak/</t>
+  </si>
+  <si>
+    <t>http://talkingstickresort.com/</t>
+  </si>
+  <si>
+    <t>https://www.marriott.com/hotels/travel/phxlc-the-phoenician-a-luxury-collection-resort-scottsdale/</t>
+  </si>
+  <si>
+    <t>http://www.hilton.com/en/hotels/phxssqq-the-scottsdale-resort-and-spa/</t>
+  </si>
+  <si>
+    <t>https://www.grandsierraresort.com/</t>
+  </si>
+  <si>
+    <t>https://www.peppermillreno.com/</t>
+  </si>
+  <si>
+    <t>https://www.marriott.com/en-us/hotels/ausbr-downright-austin-a-renaissance-hotel/overview/?scid=f2ae0541-1279-4f24-b197-a979c79310b0</t>
+  </si>
+  <si>
+    <t>https://hsbresort.com/</t>
+  </si>
+  <si>
+    <t>https://www.hyatt.com/en-US/hotel/texas/hyatt-regency-lost-pines-resort-and-spa/auslp</t>
+  </si>
+  <si>
+    <t>https://www.omnihotels.com/hotels/austin-barton-creek</t>
+  </si>
+  <si>
+    <t>http://www.omnihotels.com/frisco</t>
+  </si>
+  <si>
+    <t>https://www.omnihotels.com/hotels/dallas-las-colinas?utm_source=gmblisting&amp;utm_medium=organic</t>
+  </si>
+  <si>
+    <t>https://www.omnihotels.com/hotels/pga-frisco</t>
+  </si>
+  <si>
+    <t>https://www.hyatt.com/hotel/texas/thompson-houston/iahth?icamp=hpe_hycom</t>
+  </si>
+  <si>
+    <t>https://www.hyatt.com/en-US/hotel/texas/grand-hyatt-san-antonio-river-walk/satgh</t>
+  </si>
+  <si>
+    <t>http://sanantonio.regency.hyatt.com/</t>
+  </si>
+  <si>
+    <t>http://www.hilton.com/en/hotels/satcnsa-signia-la-cantera-resort-and-spa/</t>
+  </si>
+  <si>
+    <t>http://www.marriott.com/satvw</t>
+  </si>
+  <si>
+    <t>http://www.scottsdaleprincess.com/</t>
+  </si>
+  <si>
+    <t>https://playatgila.com/meetings/</t>
+  </si>
+  <si>
+    <t>https://www.wigwamarizona.com/</t>
+  </si>
+  <si>
+    <t>https://www.loewshotels.com/ventana-canyon?chebs=PARTNER_CVENT_LISTING</t>
+  </si>
+  <si>
+    <t>https://www.kalahariresorts.com/texas</t>
+  </si>
+  <si>
+    <t>http://www.hilton.com/en/hotels/dfwanhh-hilton-anatole/</t>
+  </si>
+  <si>
+    <t>https://www.ritzcarlton.com/en/hotels/dalil-the-ritz-carlton-dallas-las-colinas/overview/</t>
+  </si>
+  <si>
+    <t>https://www.sonesta.com/us/texas/houston/royal-sonesta-houston-galleria</t>
+  </si>
+  <si>
+    <t>http://www.hilton.com/en/hotels/iahwrqq-the-woodlands-resort/</t>
+  </si>
 </sst>
 </file>
 
@@ -9101,7 +9185,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -9174,6 +9258,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -9323,15 +9414,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -9423,12 +9515,22 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Comma" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
     <cellStyle name="Comma [0]" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
     <cellStyle name="Currency" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Currency [0]" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
@@ -12790,92 +12892,92 @@
       <c r="A13" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="H13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="I13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="N13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="O13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="P13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="R13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="S13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="T13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="U13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="V13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="W13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="X13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AA13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AC13" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD13" s="14" t="s">
-        <v>74</v>
+      <c r="B13" s="31" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>1963</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>1965</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>1966</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>1967</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>1968</v>
+      </c>
+      <c r="I13" s="31" t="s">
+        <v>1969</v>
+      </c>
+      <c r="J13" s="31" t="s">
+        <v>1970</v>
+      </c>
+      <c r="K13" s="31" t="s">
+        <v>1943</v>
+      </c>
+      <c r="L13" s="32" t="s">
+        <v>1944</v>
+      </c>
+      <c r="M13" s="33" t="s">
+        <v>1945</v>
+      </c>
+      <c r="N13" s="33" t="s">
+        <v>1946</v>
+      </c>
+      <c r="O13" s="33" t="s">
+        <v>1947</v>
+      </c>
+      <c r="P13" s="33" t="s">
+        <v>1948</v>
+      </c>
+      <c r="Q13" s="33" t="s">
+        <v>1949</v>
+      </c>
+      <c r="R13" s="33" t="s">
+        <v>1950</v>
+      </c>
+      <c r="S13" s="33" t="s">
+        <v>1951</v>
+      </c>
+      <c r="T13" s="33" t="s">
+        <v>1952</v>
+      </c>
+      <c r="U13" s="33" t="s">
+        <v>1953</v>
+      </c>
+      <c r="V13" s="33" t="s">
+        <v>1953</v>
+      </c>
+      <c r="W13" s="33" t="s">
+        <v>1954</v>
+      </c>
+      <c r="X13" s="33" t="s">
+        <v>1955</v>
+      </c>
+      <c r="Y13" s="33" t="s">
+        <v>1956</v>
+      </c>
+      <c r="Z13" s="33" t="s">
+        <v>1957</v>
+      </c>
+      <c r="AA13" s="33" t="s">
+        <v>1958</v>
+      </c>
+      <c r="AB13" s="33" t="s">
+        <v>1959</v>
+      </c>
+      <c r="AC13" s="33" t="s">
+        <v>1960</v>
+      </c>
+      <c r="AD13" s="33" t="s">
+        <v>1961</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="99.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/NSM_IBSA_2028.xlsx
+++ b/NSM_IBSA_2028.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francesco/DocEvents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{641BE98C-39E1-754A-A9FB-631BDEA7A99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32488A08-E5CA-994D-9A2B-2DF1EF976AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1120" windowWidth="35600" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2720" yWindow="3600" windowWidth="35600" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Submitted proposal" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4567" uniqueCount="1971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4568" uniqueCount="1971">
   <si>
     <t>NSM IBSA 2028</t>
   </si>
@@ -15622,7 +15622,9 @@
       <c r="Q48" s="25" t="s">
         <v>463</v>
       </c>
-      <c r="R48" s="25"/>
+      <c r="R48" s="25" t="s">
+        <v>493</v>
+      </c>
       <c r="S48" s="25" t="s">
         <v>464</v>
       </c>
@@ -16276,57 +16278,57 @@
       </c>
       <c r="AD57" s="7"/>
     </row>
-    <row r="58" spans="1:30" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="3" t="s">
+    <row r="58" spans="1:30" s="27" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A58" s="22" t="s">
         <v>543</v>
       </c>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
-      <c r="G58" s="11"/>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11" t="s">
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="23"/>
+      <c r="H58" s="23"/>
+      <c r="I58" s="23" t="s">
         <v>456</v>
       </c>
-      <c r="J58" s="11"/>
-      <c r="K58" s="11" t="s">
+      <c r="J58" s="23"/>
+      <c r="K58" s="23" t="s">
         <v>544</v>
       </c>
-      <c r="L58" s="5"/>
-      <c r="M58" s="7"/>
-      <c r="N58" s="8" t="s">
+      <c r="L58" s="29"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="25" t="s">
         <v>558</v>
       </c>
-      <c r="O58" s="7"/>
-      <c r="P58" s="8" t="s">
+      <c r="O58" s="26"/>
+      <c r="P58" s="25" t="s">
         <v>545</v>
       </c>
-      <c r="Q58" s="7"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="8" t="s">
+      <c r="Q58" s="26"/>
+      <c r="R58" s="26"/>
+      <c r="S58" s="25" t="s">
         <v>546</v>
       </c>
-      <c r="T58" s="8" t="s">
+      <c r="T58" s="25" t="s">
         <v>547</v>
       </c>
-      <c r="U58" s="8" t="s">
+      <c r="U58" s="25" t="s">
         <v>548</v>
       </c>
-      <c r="V58" s="7"/>
-      <c r="W58" s="8" t="s">
+      <c r="V58" s="26"/>
+      <c r="W58" s="25" t="s">
         <v>455</v>
       </c>
-      <c r="X58" s="7"/>
-      <c r="Y58" s="8" t="s">
+      <c r="X58" s="26"/>
+      <c r="Y58" s="25" t="s">
         <v>549</v>
       </c>
-      <c r="Z58" s="7"/>
-      <c r="AA58" s="7"/>
-      <c r="AB58" s="7"/>
-      <c r="AC58" s="8"/>
-      <c r="AD58" s="7"/>
+      <c r="Z58" s="26"/>
+      <c r="AA58" s="26"/>
+      <c r="AB58" s="26"/>
+      <c r="AC58" s="25"/>
+      <c r="AD58" s="26"/>
     </row>
     <row r="59" spans="1:30" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3" t="s">

--- a/NSM_IBSA_2028.xlsx
+++ b/NSM_IBSA_2028.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/francesco/DocEvents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32488A08-E5CA-994D-9A2B-2DF1EF976AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B25BA7-55B6-E34F-AB89-B40E034688AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2720" yWindow="3600" windowWidth="35600" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2180" yWindow="2000" windowWidth="27540" windowHeight="20480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Submitted proposal" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4568" uniqueCount="1971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4569" uniqueCount="1971">
   <si>
     <t>NSM IBSA 2028</t>
   </si>
@@ -14060,95 +14060,95 @@
         <v>293</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:30" s="27" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="J27" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="K27" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="L27" s="24" t="s">
         <v>296</v>
       </c>
-      <c r="M27" s="8" t="s">
+      <c r="M27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="N27" s="8" t="s">
+      <c r="N27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="O27" s="8" t="s">
+      <c r="O27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="P27" s="8" t="s">
+      <c r="P27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="Q27" s="18" t="s">
+      <c r="Q27" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="R27" s="8" t="s">
+      <c r="R27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="S27" s="8" t="s">
+      <c r="S27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="T27" s="8" t="s">
+      <c r="T27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="U27" s="8" t="s">
+      <c r="U27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="V27" s="8" t="s">
+      <c r="V27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="W27" s="8" t="s">
+      <c r="W27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="X27" s="8" t="s">
+      <c r="X27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="Y27" s="8" t="s">
+      <c r="Y27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="Z27" s="8" t="s">
+      <c r="Z27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="AA27" s="8" t="s">
+      <c r="AA27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="AB27" s="8" t="s">
+      <c r="AB27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="AC27" s="8" t="s">
+      <c r="AC27" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="AD27" s="8" t="s">
+      <c r="AD27" s="25" t="s">
         <v>296</v>
       </c>
     </row>
@@ -15613,7 +15613,9 @@
       <c r="L48" s="24" t="s">
         <v>461</v>
       </c>
-      <c r="M48" s="25"/>
+      <c r="M48" s="8" t="s">
+        <v>490</v>
+      </c>
       <c r="N48" s="26"/>
       <c r="O48" s="25" t="s">
         <v>462</v>
